--- a/data/trans_bre/IP2002-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP2002-Edad-trans_bre.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 0,0</t>
+          <t>-6,83; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,54</t>
+          <t>-1,9; 1,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 1,16</t>
+          <t>-4,78; 1,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 3,73</t>
+          <t>-0,18; 3,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 2,79</t>
+          <t>-4,08; 2,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-81,57; 371,9</t>
+          <t>-81,23; 242,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-76,83; 52,88</t>
+          <t>-80,05; 53,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,27; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-73,26; 151,06</t>
+          <t>-68,67; 144,46</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 3,17</t>
+          <t>-9,57; 3,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 3,47</t>
+          <t>-7,72; 3,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 8,11</t>
+          <t>-1,49; 8,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 9,16</t>
+          <t>0,1; 9,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-54,14; 30,87</t>
+          <t>-54,84; 38,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-58,45; 40,45</t>
+          <t>-54,16; 48,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 164,65</t>
+          <t>-16,87; 169,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 274,3</t>
+          <t>-3,76; 318,18</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 7,4</t>
+          <t>-3,86; 7,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 4,29</t>
+          <t>-6,75; 4,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 3,93</t>
+          <t>-7,03; 4,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 4,2</t>
+          <t>-3,88; 4,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 73,94</t>
+          <t>-25,15; 77,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,17; 55,71</t>
+          <t>-47,91; 61,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,22; 53,11</t>
+          <t>-49,52; 65,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,57; 88,42</t>
+          <t>-47,44; 96,16</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 2,17</t>
+          <t>-2,69; 2,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 0,86</t>
+          <t>-3,83; 0,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,61</t>
+          <t>-0,6; 3,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 3,05</t>
+          <t>-1,25; 3,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,84; 36,18</t>
+          <t>-32,34; 32,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-45,24; 15,49</t>
+          <t>-46,34; 13,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 94,65</t>
+          <t>-10,23; 87,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-25,29; 71,79</t>
+          <t>-21,13; 84,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2002-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP2002-Edad-trans_bre.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 0,0</t>
+          <t>-7,62; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,69</t>
+          <t>-2,04; 1,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 1,02</t>
+          <t>-4,62; 0,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,75</t>
+          <t>-0,33; 3,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 2,84</t>
+          <t>-3,98; 2,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-81,23; 242,47</t>
+          <t>-84,35; 222,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,05; 53,63</t>
+          <t>-76,75; 50,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-54,63; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,67; 144,46</t>
+          <t>-70,15; 168,85</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 3,97</t>
+          <t>-9,82; 4,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 3,72</t>
+          <t>-7,55; 3,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 8,25</t>
+          <t>-1,45; 7,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 9,68</t>
+          <t>-0,33; 8,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-54,84; 38,44</t>
+          <t>-52,98; 43,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-54,16; 48,29</t>
+          <t>-54,65; 51,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,87; 169,31</t>
+          <t>-17,26; 161,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 318,18</t>
+          <t>-8,63; 272,33</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 7,17</t>
+          <t>-3,74; 7,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 4,81</t>
+          <t>-6,83; 3,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 4,52</t>
+          <t>-6,0; 3,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 4,04</t>
+          <t>-3,99; 4,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,15; 77,31</t>
+          <t>-25,25; 78,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,91; 61,43</t>
+          <t>-48,61; 43,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,52; 65,3</t>
+          <t>-47,4; 53,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,44; 96,16</t>
+          <t>-51,58; 92,96</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 2,01</t>
+          <t>-2,35; 2,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 0,73</t>
+          <t>-3,52; 0,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 3,49</t>
+          <t>-0,75; 3,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,24</t>
+          <t>-1,33; 2,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-32,34; 32,61</t>
+          <t>-28,22; 37,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-46,34; 13,19</t>
+          <t>-43,91; 14,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 87,79</t>
+          <t>-14,0; 85,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 84,68</t>
+          <t>-21,94; 72,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2002-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP2002-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,48</t>
+          <t>-1,42</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 0,0</t>
+          <t>-6,28; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-0,21</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-11,67%</t>
+          <t>-5,32%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 1,58</t>
+          <t>-1,9; 1,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 0,93</t>
+          <t>-4,55; 1,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 3,64</t>
+          <t>-0,34; 3,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 2,79</t>
+          <t>-3,93; 3,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-84,35; 222,57</t>
+          <t>-81,57; 371,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-76,75; 50,22</t>
+          <t>-76,83; 52,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-54,63; —</t>
+          <t>-58,27; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,15; 168,85</t>
+          <t>-73,49; 165,67</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,27</t>
+          <t>4,51</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 4,46</t>
+          <t>-9,57; 3,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 3,58</t>
+          <t>-8,1; 3,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 7,92</t>
+          <t>-1,62; 8,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 8,94</t>
+          <t>-0,12; 9,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-52,98; 43,54</t>
+          <t>-54,14; 30,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-54,65; 51,69</t>
+          <t>-58,45; 40,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,26; 161,46</t>
+          <t>-15,91; 164,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 272,33</t>
+          <t>-11,74; 290,11</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 7,25</t>
+          <t>-3,83; 7,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 3,97</t>
+          <t>-6,43; 4,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 3,96</t>
+          <t>-5,97; 3,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 4,23</t>
+          <t>-3,33; 4,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 78,19</t>
+          <t>-26,14; 73,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,61; 43,52</t>
+          <t>-46,17; 55,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,4; 53,97</t>
+          <t>-45,22; 53,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-51,58; 92,96</t>
+          <t>-42,5; 103,54</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>1,19</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 2,21</t>
+          <t>-2,56; 2,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,83</t>
+          <t>-3,73; 0,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,43</t>
+          <t>-0,67; 3,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,95</t>
+          <t>-1,29; 3,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,22; 37,15</t>
+          <t>-30,84; 36,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-43,91; 14,26</t>
+          <t>-45,24; 15,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 85,88</t>
+          <t>-12,57; 94,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 72,81</t>
+          <t>-20,55; 81,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2002-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP2002-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,42</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-1.423874161784973</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-6,28; 0,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>-6.282328146290596</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,71</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,45</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-12,28%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-40,69%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>179,53%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-5,32%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,9; 1,54</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,55; 1,16</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-0,34; 3,73</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-3,93; 3,34</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-81,57; 371,9</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-76,83; 52,88</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-58,27; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-73,49; 165,67</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.1991682812768467</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.711995244995558</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.454243709992518</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.2057345878461826</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1228430631873535</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.4068739075723244</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>1.79533741228844</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.05324744669479645</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-2,59</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,25</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,31</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,51</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-17,91%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-20,53%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>46,26%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>94,35%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.904011584616952</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.549255496600757</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.3442067308137746</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.925861765653242</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.8156611821772539</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.7683025751588589</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.5826866282584502</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.7349370936497835</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-9,57; 3,17</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-8,1; 3,47</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,62; 8,11</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-0,12; 9,41</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-54,14; 30,87</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-58,45; 40,45</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-15,91; 164,65</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-11,74; 290,11</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.540353929192795</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.157127889170189</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.728070969409185</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.337876988477146</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>3.718976989041727</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.5287720956531735</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="n">
+        <v>1.656724424440425</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +783,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,63</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,13</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,91</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,34</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,27%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-10,18%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-8,72%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-2.59352250492307</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.253787435289284</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>3.308250951297335</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>4.51428416501983</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.1790920479386156</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.20530787860529</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.4626392744606107</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.9435181734314829</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,83; 7,4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-6,43; 4,29</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-5,97; 3,93</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-3,33; 4,19</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-26,14; 73,94</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-46,17; 55,71</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-45,22; 53,11</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-42,5; 103,54</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-9.574715472257989</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-8.100209718875558</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.618549698922536</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-0.1221285136512305</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.5414081501846719</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.5844859300469416</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.159129168023629</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.1174169377320358</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3.172099309709073</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.46830235301484</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>8.112027198714785</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>9.40950005194308</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.3086645447060131</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.4044596043628074</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.646462847391155</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>2.901065468487471</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.633388340539276</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.134092581340274</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.9088832749078637</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.3379621590473579</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1326779601539455</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1018418221354031</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.08719729488897632</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.05464774233239333</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3.828911761262468</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-6.430357587104471</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-5.974256838203035</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-3.327174457111574</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2614412564908727</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4617108127153061</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.4522357289107859</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.4250176031361662</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>7.397696107391905</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.286361605893743</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.934209974976156</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>4.187006567627646</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.739433860585703</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.5570606007682172</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.531129903883245</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.03543339140852</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-1,4</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,44%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-20,15%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>29,16%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>23,92%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,56; 2,17</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,73; 0,86</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,67; 3,61</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,29; 3,28</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-30,84; 36,18</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-45,24; 15,49</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-12,57; 94,65</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-20,55; 81,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.1777268367883514</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-1.395986701484052</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.402504110776862</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.19017431274183</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.02440856104867754</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.2014960809089524</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.2915529311512513</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.2391806891001438</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.561496213520331</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.728112116182426</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.6731146281087408</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.286474596661024</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.3083854576222361</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.452389747844769</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.125654092743635</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.2055199388439939</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.172586648884698</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.8633540679179137</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.61371364061364</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.281693127734554</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.3618426206181263</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.1548699664372181</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.9465367714625371</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.8138331365737015</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1081,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
